--- a/data/trans_orig/P15D$nada-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P15D$nada-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2663</t>
+          <t>2515</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10558</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>47,19%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5343</t>
+          <t>4893</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>30,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3795</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,01%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9539</t>
+          <t>8722</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,87%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5112</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>2375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>11549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7810</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17113</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6968</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>17102</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29667</t>
+          <t>29596</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>76,58%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4743</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5130</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>15,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2179</t>
+          <t>2975</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3712</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>14382</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8100</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>21730</t>
+          <t>22543</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1814</t>
+          <t>1825</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9807</t>
+          <t>10075</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1094</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4886</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>16446</t>
+          <t>16059</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16622</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29609</t>
+          <t>30638</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>71,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>11484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22872</t>
+          <t>22840</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,83%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32340</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49303</t>
+          <t>49977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,35%</t>
+          <t>43,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,62%</t>
+          <t>68,54%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14805</t>
+          <t>15205</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3317</t>
+          <t>3996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15696</t>
+          <t>15894</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,8%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>4653</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14053</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>938</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6838</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18036</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>38,99%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>1963</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10428</t>
+          <t>11194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5415</t>
+          <t>4452</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2928</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>26,49%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,37%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12784</t>
+          <t>13364</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21560</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>55,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>14428</t>
+          <t>15387</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>28940</t>
+          <t>28617</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>59,72%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2072</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11231</t>
+          <t>10908</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6266</t>
+          <t>5388</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>14135</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>27,81%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6320</t>
+          <t>6242</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17528</t>
+          <t>17323</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>51,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7217</t>
+          <t>7475</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>22348</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,93%</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5487</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2234,7 +2234,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10031</t>
+          <t>10595</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2462</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>12347</t>
+          <t>13740</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,51%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>11213</t>
+          <t>11215</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22741</t>
+          <t>22734</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,46%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8612</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18707</t>
+          <t>18402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>78,97%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>23424</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>38529</t>
+          <t>38309</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,74%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8256</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6487</t>
+          <t>6195</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>12189</t>
+          <t>11936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>23046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42545</t>
+          <t>42555</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>9318</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23607</t>
+          <t>24120</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60982</t>
+          <t>61094</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10013</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24879</t>
+          <t>25623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>6823</t>
+          <t>6149</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>20042</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>19210</t>
+          <t>19114</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>40138</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>17,68%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46445</t>
+          <t>45632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68865</t>
+          <t>68392</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,74%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>51379</t>
+          <t>50824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>70627</t>
+          <t>69211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>75,29%</t>
+          <t>73,78%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101500</t>
+          <t>103625</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>133121</t>
+          <t>132591</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>61,13%</t>
         </is>
       </c>
     </row>
@@ -2896,12 +2896,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10271</t>
+          <t>9806</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>27330</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2911,12 +2911,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1882</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>10619</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,12 +2966,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14495</t>
+          <t>14220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>33396</t>
+          <t>33122</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2981,12 +2981,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6305</t>
+          <t>6320</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17898</t>
+          <t>18028</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,32%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16761</t>
+          <t>17550</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34482</t>
+          <t>35036</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5250</t>
+          <t>5101</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>999</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9188</t>
+          <t>9960</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10969</t>
+          <t>10897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,77%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>32313</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>46091</t>
+          <t>46640</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>36970</t>
+          <t>37762</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>58987</t>
+          <t>59426</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>79446</t>
+          <t>79281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -3584,12 +3584,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3206</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12806</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3599,12 +3599,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,54%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3619,12 +3619,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1148</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10211</t>
+          <t>9858</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3634,12 +3634,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3654,12 +3654,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5562</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>18672</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3669,12 +3669,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11018</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25770</t>
+          <t>27575</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11120</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>26501</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>24401</t>
+          <t>26005</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46557</t>
+          <t>47430</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>31,28%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2331</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12818</t>
+          <t>12822</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14802</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>8732</t>
+          <t>8315</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23718</t>
+          <t>23098</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41454</t>
+          <t>41308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>58865</t>
+          <t>59620</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,44%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29329</t>
+          <t>29717</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46578</t>
+          <t>46291</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77672</t>
+          <t>75960</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>101668</t>
+          <t>100948</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>66,58%</t>
         </is>
       </c>
     </row>
@@ -4040,12 +4040,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1100</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9370</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,12 +4055,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4075,12 +4075,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4239</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14976</t>
+          <t>15654</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6656</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5611</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17563</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21167</t>
+          <t>20652</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16178</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>33479</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,53%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2302</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12643</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4310,7 +4310,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4929</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2837</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13350</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,8%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25964</t>
+          <t>24992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>40301</t>
+          <t>40696</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29601</t>
+          <t>29886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43931</t>
+          <t>44733</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>52,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>60137</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80893</t>
+          <t>79995</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>69,86%</t>
         </is>
       </c>
     </row>
@@ -4496,12 +4496,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3391</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4511,12 +4511,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4531,12 +4531,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>11572</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7274</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20660</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22101</t>
+          <t>23089</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41315</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>18886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35721</t>
+          <t>36347</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>50,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45821</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71528</t>
+          <t>72388</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>45,1%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4591</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16687</t>
+          <t>17970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,92%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3888</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15938</t>
+          <t>16150</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10928</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28565</t>
+          <t>27858</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32957</t>
+          <t>32054</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>52492</t>
+          <t>51584</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,34%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>59,51%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25743</t>
+          <t>25288</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>63951</t>
+          <t>63116</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>90924</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>56,2%</t>
         </is>
       </c>
     </row>
@@ -4952,12 +4952,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1833</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12929</t>
+          <t>12324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2932</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14827</t>
+          <t>15604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56722</t>
+          <t>56671</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>87176</t>
+          <t>86248</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>56893</t>
+          <t>58345</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>87597</t>
+          <t>87992</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122858</t>
+          <t>123051</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>162758</t>
+          <t>165548</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14526</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33785</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13536</t>
+          <t>13971</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>31420</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>32422</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>60169</t>
+          <t>60281</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>149176</t>
+          <t>146400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181649</t>
+          <t>181897</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>64,01%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>125526</t>
+          <t>123411</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>158211</t>
+          <t>153519</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,2%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>284961</t>
+          <t>281031</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>331171</t>
+          <t>329930</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,31%</t>
         </is>
       </c>
     </row>
@@ -5408,12 +5408,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15800</t>
+          <t>15444</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35781</t>
+          <t>35229</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>13537</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31099</t>
+          <t>30608</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5458,12 +5458,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>32517</t>
+          <t>32220</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>58572</t>
+          <t>57975</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5493,12 +5493,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13080</t>
+          <t>13104</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>9094</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6249</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18971</t>
+          <t>18735</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1642</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8839</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3110</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>13195</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>17191</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>19,99%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>19936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31644</t>
+          <t>31228</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,91%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>76,06%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24128</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37788</t>
+          <t>37464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>77,63%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>47192</t>
+          <t>48093</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>65459</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,27%</t>
+          <t>53,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>72,35%</t>
         </is>
       </c>
     </row>
@@ -6096,12 +6096,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8977</t>
+          <t>9065</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2485</t>
+          <t>3014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12822</t>
+          <t>13092</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5612</t>
+          <t>5991</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6181,12 +6181,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3771</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14815</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4358</t>
+          <t>4191</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>33,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10727</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>25738</t>
+          <t>25269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>4198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16171</t>
+          <t>15140</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2547</t>
+          <t>2236</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13560</t>
+          <t>12295</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,6%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>9243</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>23503</t>
+          <t>22826</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>21,16%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25963</t>
+          <t>26737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42008</t>
+          <t>42630</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>18762</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32797</t>
+          <t>32795</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>39,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49482</t>
+          <t>49758</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>70704</t>
+          <t>69934</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,86%</t>
+          <t>46,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>64,82%</t>
         </is>
       </c>
     </row>
@@ -6552,12 +6552,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4134</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>15897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6567,12 +6567,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6587,12 +6587,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3178</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14689</t>
+          <t>14377</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6602,12 +6602,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6622,12 +6622,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>26046</t>
+          <t>26682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6637,12 +6637,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,73%</t>
         </is>
       </c>
     </row>
@@ -6669,12 +6669,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11791</t>
+          <t>11972</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>32,16%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4173</t>
+          <t>4202</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>14602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8650</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23539</t>
+          <t>22915</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>33,59%</t>
         </is>
       </c>
     </row>
@@ -6787,7 +6787,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6218</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6802,7 +6802,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7027</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>18660</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30191</t>
+          <t>30115</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14344</t>
+          <t>14867</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>26035</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,45%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36913</t>
+          <t>36371</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53257</t>
+          <t>52632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>54,1%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8915</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6649</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7063,7 +7063,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2102</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>11833</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>5794</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1328</t>
+          <t>1711</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12997</t>
+          <t>15488</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>9698</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26491</t>
+          <t>25248</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,44%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5197</t>
+          <t>4924</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16760</t>
+          <t>16689</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2060</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12277</t>
+          <t>12071</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25503</t>
+          <t>25852</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>20,93%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28148</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44214</t>
+          <t>44215</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>37763</t>
+          <t>37924</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>53340</t>
+          <t>52463</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>70278</t>
+          <t>70759</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>92242</t>
+          <t>92225</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,69%</t>
+          <t>74,67%</t>
         </is>
       </c>
     </row>
@@ -7464,12 +7464,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12416</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7479,12 +7479,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7499,12 +7499,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10915</t>
+          <t>11437</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7514,12 +7514,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7534,12 +7534,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5144</t>
+          <t>4983</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>17824</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7549,12 +7549,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,43%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>23303</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>44501</t>
+          <t>44783</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18046</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>38099</t>
+          <t>37960</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>46519</t>
+          <t>45605</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>74381</t>
+          <t>74175</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,02%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17558</t>
+          <t>17590</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36131</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12618</t>
+          <t>11592</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>29936</t>
+          <t>29343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>33532</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57282</t>
+          <t>59360</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>107727</t>
+          <t>106898</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135418</t>
+          <t>135360</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>109543</t>
+          <t>109229</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136873</t>
+          <t>136949</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>226554</t>
+          <t>224871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>266569</t>
+          <t>263315</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,37%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -7920,12 +7920,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32869</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7955,12 +7955,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12332</t>
+          <t>13168</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>30864</t>
+          <t>32182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7990,12 +7990,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31206</t>
+          <t>31789</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57173</t>
+          <t>56715</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8005,12 +8005,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7549</t>
+          <t>7751</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3681</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12895</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7603</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15153</t>
+          <t>15506</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10316</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22783</t>
+          <t>22750</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5403</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2306</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7646</t>
+          <t>7934</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4276</t>
+          <t>4217</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12656</t>
+          <t>13292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>13049</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>7727</t>
+          <t>7995</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19390</t>
+          <t>21394</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,14%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17259</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31121</t>
+          <t>35004</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>22153</t>
+          <t>24539</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>19322</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26572</t>
+          <t>29504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>46516</t>
+          <t>52245</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>37761</t>
+          <t>42949</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>54274</t>
+          <t>62600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>64,8%</t>
         </is>
       </c>
     </row>
@@ -8603,32 +8603,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7565</t>
+          <t>8425</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3582</t>
+          <t>4402</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13084</t>
+          <t>15300</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8638,32 +8638,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5840</t>
+          <t>6693</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3287</t>
+          <t>3910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9004</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8673,32 +8673,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>13406</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8782</t>
+          <t>9432</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>22637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>23,43%</t>
         </is>
       </c>
     </row>
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13520</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>22638</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13338</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7983</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27076</t>
+          <t>26858</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>18428</t>
+          <t>17551</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>37306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>27,11%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5979</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2675</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14009</t>
+          <t>13118</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9411</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>14626</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,32 +8903,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>15390</t>
+          <t>16973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10629</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24564</t>
+          <t>24343</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>34364</t>
+          <t>40556</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24398</t>
+          <t>29653</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>39,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,1%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>27231</t>
+          <t>30849</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20383</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34689</t>
+          <t>38098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>61594</t>
+          <t>71405</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>58116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73817</t>
+          <t>83837</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>51,89%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,5%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -9059,32 +9059,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12834</t>
+          <t>14181</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>7262</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22756</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>18,96%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9094,32 +9094,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7399</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>32,03%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9129,32 +9129,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>20233</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12289</t>
+          <t>13635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32858</t>
+          <t>36232</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,26%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -9176,32 +9176,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4395</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>994</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9901</t>
+          <t>9309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,39%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7196</t>
+          <t>7695</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12695</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>25,66%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>11591</t>
+          <t>11781</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6437</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18523</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -9289,7 +9289,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4512</t>
+          <t>5916</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>17,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>11246</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6292</t>
+          <t>7076</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16166</t>
+          <t>17208</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>13089</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6785</t>
+          <t>8123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>20021</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>24,28%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>18408</t>
+          <t>21358</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12659</t>
+          <t>15435</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>22703</t>
+          <t>26153</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>64,78%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22713</t>
+          <t>26416</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17330</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27962</t>
+          <t>32856</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41121</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32940</t>
+          <t>38302</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>48998</t>
+          <t>55737</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>57,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>67,6%</t>
         </is>
       </c>
     </row>
@@ -9515,32 +9515,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>5213</t>
+          <t>5684</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2218</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>11089</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9550,32 +9550,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3843</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1541</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8329</t>
+          <t>9487</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9585,32 +9585,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4913</t>
+          <t>5630</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15291</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>19,74%</t>
         </is>
       </c>
     </row>
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7243</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4369</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13050</t>
+          <t>14914</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,16%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>13596</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9165</t>
+          <t>9285</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18703</t>
+          <t>19651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>20839</t>
+          <t>22616</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14983</t>
+          <t>15975</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>28546</t>
+          <t>30999</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4638</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>964</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14809</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>12338</t>
+          <t>12658</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7504</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19270</t>
+          <t>19225</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>16897</t>
+          <t>17296</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10780</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27107</t>
+          <t>27291</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>19,99%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>40623</t>
+          <t>42695</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32044</t>
+          <t>34521</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47222</t>
+          <t>50173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>80,19%</t>
+          <t>78,95%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>36165</t>
+          <t>38308</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29079</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>42914</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>52,4%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>76788</t>
+          <t>81003</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66198</t>
+          <t>68805</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>86648</t>
+          <t>90021</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>65,94%</t>
         </is>
       </c>
     </row>
@@ -9971,32 +9971,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>7710</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2767</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12976</t>
+          <t>14413</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10006,32 +10006,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6919</t>
+          <t>7895</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>12692</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10041,32 +10041,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13380</t>
+          <t>15605</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8493</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20349</t>
+          <t>24242</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>17,76%</t>
         </is>
       </c>
     </row>
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>33861</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23395</t>
+          <t>24518</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46013</t>
+          <t>46864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>41588</t>
+          <t>42901</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33063</t>
+          <t>33584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>52911</t>
+          <t>52788</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>74658</t>
+          <t>76762</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>61252</t>
+          <t>63985</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>91050</t>
+          <t>92485</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>17157</t>
+          <t>18847</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29251</t>
+          <t>30416</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39751</t>
+          <t>42255</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>30958</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>53568</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>18,61%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>56908</t>
+          <t>61101</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45885</t>
+          <t>48231</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>71479</t>
+          <t>77018</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,99%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>117758</t>
+          <t>132316</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>101920</t>
+          <t>115781</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>132688</t>
+          <t>146970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>66,32%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>108262</t>
+          <t>120111</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>95708</t>
+          <t>106555</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120943</t>
+          <t>133540</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>226020</t>
+          <t>252427</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>207018</t>
+          <t>230300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>248835</t>
+          <t>272390</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -10427,32 +10427,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>32074</t>
+          <t>36000</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22408</t>
+          <t>25581</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49570</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10462,32 +10462,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>24002</t>
+          <t>26913</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>36713</t>
+          <t>38188</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10497,32 +10497,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>62913</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44812</t>
+          <t>50546</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72856</t>
+          <t>80578</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,78%</t>
         </is>
       </c>
     </row>
